--- a/Monitoría 202601.xlsx
+++ b/Monitoría 202601.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\OneDrive\Escritorio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\OneDrive\Escritorio\Monitoria-202601\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85621929-055E-410E-A7DB-5FA5E9F945F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67E5EF0-7D05-4698-8D2B-013376C5881F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C32DDC5-944F-4023-957D-E29A0EB9D475}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
   <si>
     <t>Semana</t>
   </si>
@@ -150,9 +150,6 @@
   </si>
   <si>
     <t>Matplotlib, Seaborn y Folium a fondo</t>
-  </si>
-  <si>
-    <t>Obtención de datos de APIs abiertas, interactuar con IA desde Python</t>
   </si>
   <si>
     <t>Redes neuronales</t>
@@ -197,12 +194,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -243,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -257,6 +260,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -619,12 +623,12 @@
       </c>
       <c r="C3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46063</v>
+        <v>46119</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>19</v>
       </c>
     </row>
@@ -634,12 +638,12 @@
       </c>
       <c r="C4" s="4">
         <f ca="1">+C3+7</f>
-        <v>46070</v>
+        <v>46126</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -649,13 +653,13 @@
       </c>
       <c r="C5" s="4">
         <f t="shared" ref="C5:C19" ca="1" si="0">+C4+7</f>
-        <v>46077</v>
+        <v>46133</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>43</v>
+      <c r="E5" s="7" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -664,12 +668,12 @@
       </c>
       <c r="C6" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46084</v>
+        <v>46140</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>22</v>
       </c>
     </row>
@@ -679,12 +683,12 @@
       </c>
       <c r="C7" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46091</v>
+        <v>46147</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>36</v>
       </c>
     </row>
@@ -694,10 +698,10 @@
       </c>
       <c r="C8" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46098</v>
+        <v>46154</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>37</v>
@@ -709,13 +713,13 @@
       </c>
       <c r="C9" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46105</v>
+        <v>46161</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
@@ -724,13 +728,13 @@
       </c>
       <c r="C10" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46112</v>
+        <v>46168</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -739,7 +743,7 @@
       </c>
       <c r="C11" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46119</v>
+        <v>46175</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>25</v>
@@ -754,7 +758,7 @@
       </c>
       <c r="C12" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46126</v>
+        <v>46182</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>26</v>
@@ -769,7 +773,7 @@
       </c>
       <c r="C13" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46133</v>
+        <v>46189</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>27</v>
@@ -784,7 +788,7 @@
       </c>
       <c r="C14" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46140</v>
+        <v>46196</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>28</v>
@@ -799,7 +803,7 @@
       </c>
       <c r="C15" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46147</v>
+        <v>46203</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>29</v>
@@ -814,13 +818,13 @@
       </c>
       <c r="C16" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46154</v>
+        <v>46210</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
@@ -829,7 +833,7 @@
       </c>
       <c r="C17" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46161</v>
+        <v>46217</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>31</v>
@@ -844,13 +848,13 @@
       </c>
       <c r="C18" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46168</v>
+        <v>46224</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
@@ -859,13 +863,13 @@
       </c>
       <c r="C19" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46175</v>
+        <v>46231</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>33</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
